--- a/corr_matrix/residual_exam3B_1PL.xlsx
+++ b/corr_matrix/residual_exam3B_1PL.xlsx
@@ -429,6 +429,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>question_id</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>3B01</t>
@@ -525,52 +530,52 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2492119409485487</v>
+        <v>0.2492050092708913</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.2064598296747395</v>
+        <v>-0.2065718110465146</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1128280348047689</v>
+        <v>-0.1129427154215756</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.136786858597422</v>
+        <v>-0.1367952775931484</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.09564128623508023</v>
+        <v>-0.09571670130777869</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.04925678004852473</v>
+        <v>-0.04936132589533832</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01815020071575849</v>
+        <v>0.01819374740410939</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4952761484343058</v>
+        <v>0.495213981730419</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.3577957329018067</v>
+        <v>-0.3577920735695569</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3072363777418384</v>
+        <v>0.3071984417133924</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2098565465510301</v>
+        <v>0.209825514643706</v>
       </c>
       <c r="N2" t="n">
-        <v>0.09408196650399329</v>
+        <v>0.09406807421767284</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.3629143792905301</v>
+        <v>-0.3629168527812306</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.240043033716194</v>
+        <v>-0.240041652478888</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.01324026375114542</v>
+        <v>-0.01330740624561528</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1259400640480613</v>
+        <v>0.1258952714727046</v>
       </c>
     </row>
     <row r="3">
@@ -580,55 +585,55 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2492119409485487</v>
+        <v>0.2492050092708913</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.09054809320739857</v>
+        <v>-0.09085791215539557</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2284841383929798</v>
+        <v>0.2282946401778682</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1634295162734284</v>
+        <v>-0.1634398208756306</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04640923226062036</v>
+        <v>0.04629510230980412</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02552542819186719</v>
+        <v>0.02542172562898728</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05826376249599678</v>
+        <v>0.05843599395875649</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.01398812487411144</v>
+        <v>-0.01396013267406331</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.109849557885149</v>
+        <v>-0.1098537172719427</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.3043262199389212</v>
+        <v>-0.3044582380897261</v>
       </c>
       <c r="M3" t="n">
-        <v>0.09898326169286588</v>
+        <v>0.09887997369014098</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1236666511412959</v>
+        <v>0.1235523167306421</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1153107941932486</v>
+        <v>0.1152318886760506</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2220477856529442</v>
+        <v>-0.2220509313305689</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1680245869612388</v>
+        <v>-0.1680519378275852</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.3191698404367023</v>
+        <v>-0.3192393180553356</v>
       </c>
     </row>
     <row r="4">
@@ -638,55 +643,55 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.2064598296747395</v>
+        <v>-0.2065718110465146</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.09054809320739857</v>
+        <v>-0.09085791215539557</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5703662707279482</v>
+        <v>0.5702285426443942</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1440125706720538</v>
+        <v>-0.144016387284289</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2445246955137508</v>
+        <v>0.2443726760703323</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.01355452865604946</v>
+        <v>-0.0137547167881814</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05613480804460625</v>
+        <v>0.05633982906553148</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.3248064728639279</v>
+        <v>-0.3248930045806256</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.2034624597536207</v>
+        <v>-0.2034565059299893</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.1479043729926314</v>
+        <v>-0.1481144841529071</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.09340833844132058</v>
+        <v>-0.09360751034880134</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1695418622051826</v>
+        <v>0.1694317149383078</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1732870349476655</v>
+        <v>0.1732404588490479</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1034063867575403</v>
+        <v>-0.1034586560844772</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2313451186971713</v>
+        <v>-0.2314742367061285</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.2014782377273373</v>
+        <v>-0.2015918916934702</v>
       </c>
     </row>
     <row r="5">
@@ -696,55 +701,55 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.1128280348047689</v>
+        <v>-0.1129427154215756</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2284841383929798</v>
+        <v>0.2282946401778682</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5703662707279482</v>
+        <v>0.5702285426443942</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1733930367383259</v>
+        <v>-0.1733848547628728</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0184801370859294</v>
+        <v>0.01826375081187321</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1277474031627356</v>
+        <v>-0.1280050313839771</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03781267606032017</v>
+        <v>0.03795022962753813</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2471656902435521</v>
+        <v>-0.2472884316464552</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.007172982808612883</v>
+        <v>-0.00706112536055262</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.2079977857330943</v>
+        <v>-0.2082233871384418</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1744470370287741</v>
+        <v>0.1742997201323452</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.02809772318126015</v>
+        <v>-0.02820518207152009</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02255237928596017</v>
+        <v>0.02253991555209153</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3009063690150895</v>
+        <v>-0.3009819188062258</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.09420577337776727</v>
+        <v>-0.0943584122147151</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.1357109229011941</v>
+        <v>-0.1358177859326537</v>
       </c>
     </row>
     <row r="6">
@@ -754,55 +759,55 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.136786858597422</v>
+        <v>-0.1367952775931484</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.1634295162734284</v>
+        <v>-0.1634398208756306</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1440125706720538</v>
+        <v>-0.144016387284289</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1733930367383259</v>
+        <v>-0.1733848547628728</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0340016981254059</v>
+        <v>-0.03390359097026611</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1879337819807184</v>
+        <v>0.1880458839961273</v>
       </c>
       <c r="I6" t="n">
-        <v>0.009015170200137769</v>
+        <v>0.009034351880312477</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2564681290403944</v>
+        <v>-0.2564580220963481</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.08206533619401084</v>
+        <v>-0.0821070805735955</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.2481790230414894</v>
+        <v>-0.2481570855462915</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2924253370046688</v>
+        <v>-0.2923604044341197</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.09969812844222496</v>
+        <v>-0.09964125034623977</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1014526443685277</v>
+        <v>-0.1014055144339805</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.06656412405046591</v>
+        <v>-0.06654841043732869</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1322972445931454</v>
+        <v>-0.1322108826535771</v>
       </c>
       <c r="R6" t="n">
-        <v>0.09091729592942735</v>
+        <v>0.09098756535788116</v>
       </c>
     </row>
     <row r="7">
@@ -812,55 +817,55 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.09564128623508023</v>
+        <v>-0.09571670130777869</v>
       </c>
       <c r="C7" t="n">
-        <v>0.04640923226062036</v>
+        <v>0.04629510230980412</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2445246955137508</v>
+        <v>0.2443726760703323</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0184801370859294</v>
+        <v>0.01826375081187321</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0340016981254059</v>
+        <v>-0.03390359097026611</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.09859147980665464</v>
+        <v>0.09851904362154286</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1630637733138994</v>
+        <v>-0.1631355942672249</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.158654416810653</v>
+        <v>-0.1586271922213337</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.09484660403731167</v>
+        <v>-0.09475055640182756</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1873325494775034</v>
+        <v>-0.187387372426345</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1104849984953841</v>
+        <v>-0.1105114871786565</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0264940950168482</v>
+        <v>-0.02649543777461131</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1039688511221221</v>
+        <v>0.1040046728592173</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.2358206499683513</v>
+        <v>-0.2357309035733321</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.07221727192292093</v>
+        <v>-0.07219477609322161</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.1757937360161807</v>
+        <v>-0.1757355241432379</v>
       </c>
     </row>
     <row r="8">
@@ -870,55 +875,55 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.04925678004852473</v>
+        <v>-0.04936132589533832</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02552542819186719</v>
+        <v>0.02542172562898728</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.01355452865604946</v>
+        <v>-0.0137547167881814</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1277474031627356</v>
+        <v>-0.1280050313839771</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1879337819807184</v>
+        <v>0.1880458839961273</v>
       </c>
       <c r="G8" t="n">
-        <v>0.09859147980665464</v>
+        <v>0.09851904362154286</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05277476660137807</v>
+        <v>0.05268434804036348</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1217934724568681</v>
+        <v>-0.1218246182652493</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1056123513784834</v>
+        <v>-0.1054883650178316</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.08420034595944915</v>
+        <v>-0.08427740359401402</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3298748988506824</v>
+        <v>-0.3299201820813433</v>
       </c>
       <c r="N8" t="n">
-        <v>0.05446596048522404</v>
+        <v>0.05451421364974728</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.06343136976200196</v>
+        <v>-0.06334297762858132</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1484123395333694</v>
+        <v>-0.1483296087384948</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1912360834919151</v>
+        <v>-0.1912657891339729</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.02440070246157641</v>
+        <v>-0.02434659855594892</v>
       </c>
     </row>
     <row r="9">
@@ -928,55 +933,55 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01815020071575849</v>
+        <v>0.01819374740410939</v>
       </c>
       <c r="C9" t="n">
-        <v>0.05826376249599678</v>
+        <v>0.05843599395875649</v>
       </c>
       <c r="D9" t="n">
-        <v>0.05613480804460625</v>
+        <v>0.05633982906553148</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03781267606032017</v>
+        <v>0.03795022962753813</v>
       </c>
       <c r="F9" t="n">
-        <v>0.009015170200137769</v>
+        <v>0.009034351880312477</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1630637733138994</v>
+        <v>-0.1631355942672249</v>
       </c>
       <c r="H9" t="n">
-        <v>0.05277476660137807</v>
+        <v>0.05268434804036348</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.242167516373171</v>
+        <v>-0.2421534706862433</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1386502627330165</v>
+        <v>-0.1383731358662313</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1927158368021573</v>
+        <v>-0.1926398572448272</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1271954123633792</v>
+        <v>-0.1271477894842661</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0578183181110305</v>
+        <v>-0.05767962334487899</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1342740350361031</v>
+        <v>0.1343683883971986</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1005609966246396</v>
+        <v>-0.1005366255512958</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.1616567900863704</v>
+        <v>-0.1617656976760998</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1070366577892605</v>
+        <v>0.1070796167322649</v>
       </c>
     </row>
     <row r="10">
@@ -986,55 +991,55 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4952761484343058</v>
+        <v>0.495213981730419</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.01398812487411144</v>
+        <v>-0.01396013267406331</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3248064728639279</v>
+        <v>-0.3248930045806256</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2471656902435521</v>
+        <v>-0.2472884316464552</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2564681290403944</v>
+        <v>-0.2564580220963481</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.158654416810653</v>
+        <v>-0.1586271922213337</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1217934724568681</v>
+        <v>-0.1218246182652493</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.242167516373171</v>
+        <v>-0.2421534706862433</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.01635828799867195</v>
+        <v>-0.01635576524283002</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2974514195609108</v>
+        <v>0.29749133915426</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1909031290530438</v>
+        <v>0.1909630549015585</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1837945865529658</v>
+        <v>0.1838161347374033</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3896350778616844</v>
+        <v>-0.3896017385194604</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.0270555951619233</v>
+        <v>-0.02692265528110705</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1450148654958565</v>
+        <v>0.1450683090663101</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.05785683486272918</v>
+        <v>-0.05781818706925114</v>
       </c>
     </row>
     <row r="11">
@@ -1044,55 +1049,55 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.3577957329018067</v>
+        <v>-0.3577920735695569</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.109849557885149</v>
+        <v>-0.1098537172719427</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2034624597536207</v>
+        <v>-0.2034565059299893</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.007172982808612883</v>
+        <v>-0.00706112536055262</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.08206533619401084</v>
+        <v>-0.0821070805735955</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.09484660403731167</v>
+        <v>-0.09475055640182756</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1056123513784834</v>
+        <v>-0.1054883650178316</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1386502627330165</v>
+        <v>-0.1383731358662313</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.01635828799867195</v>
+        <v>-0.01635576524283002</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.07252527388631944</v>
+        <v>-0.07251547254320095</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.09927759913786334</v>
+        <v>-0.09926722571402585</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1788580033863932</v>
+        <v>-0.1789118752209512</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2024258365776465</v>
+        <v>-0.2024991134970859</v>
       </c>
       <c r="P11" t="n">
-        <v>0.08871072898657484</v>
+        <v>0.08865998493314925</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.0319663306051059</v>
+        <v>0.03204375333207003</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.05027295552573411</v>
+        <v>-0.05029834336445638</v>
       </c>
     </row>
     <row r="12">
@@ -1102,55 +1107,55 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3072363777418384</v>
+        <v>0.3071984417133924</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.3043262199389212</v>
+        <v>-0.3044582380897261</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1479043729926314</v>
+        <v>-0.1481144841529071</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2079977857330943</v>
+        <v>-0.2082233871384418</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2481790230414894</v>
+        <v>-0.2481570855462915</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1873325494775034</v>
+        <v>-0.187387372426345</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.08420034595944915</v>
+        <v>-0.08427740359401402</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1927158368021573</v>
+        <v>-0.1926398572448272</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2974514195609108</v>
+        <v>0.29749133915426</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.07252527388631944</v>
+        <v>-0.07251547254320095</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>0.240494025087058</v>
+        <v>0.2404776517465995</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1329269583645311</v>
+        <v>-0.1329743527904359</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1178902286096769</v>
+        <v>-0.1179178103361963</v>
       </c>
       <c r="P12" t="n">
-        <v>0.05223704596864914</v>
+        <v>0.05231246629645079</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.1266375467447297</v>
+        <v>0.1266637001270213</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.03401914166957559</v>
+        <v>-0.03401029505711925</v>
       </c>
     </row>
     <row r="13">
@@ -1160,55 +1165,55 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2098565465510301</v>
+        <v>0.209825514643706</v>
       </c>
       <c r="C13" t="n">
-        <v>0.09898326169286588</v>
+        <v>0.09887997369014098</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.09340833844132058</v>
+        <v>-0.09360751034880134</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1744470370287741</v>
+        <v>0.1742997201323452</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2924253370046688</v>
+        <v>-0.2923604044341197</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1104849984953841</v>
+        <v>-0.1105114871786565</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.3298748988506824</v>
+        <v>-0.3299201820813433</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1271954123633792</v>
+        <v>-0.1271477894842661</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1909031290530438</v>
+        <v>0.1909630549015585</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.09927759913786334</v>
+        <v>-0.09926722571402585</v>
       </c>
       <c r="L13" t="n">
-        <v>0.240494025087058</v>
+        <v>0.2404776517465995</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.06840730406131022</v>
+        <v>-0.06843834262747379</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1930187583784253</v>
+        <v>-0.1930521382934785</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.07001011577211999</v>
+        <v>-0.06993364975982146</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.02959222950174342</v>
+        <v>0.0296466317181022</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.1713128387281347</v>
+        <v>-0.1712496303193032</v>
       </c>
     </row>
     <row r="14">
@@ -1218,55 +1223,55 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.09408196650399329</v>
+        <v>0.09406807421767284</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1236666511412959</v>
+        <v>0.1235523167306421</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1695418622051826</v>
+        <v>0.1694317149383078</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.02809772318126015</v>
+        <v>-0.02820518207152009</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.09969812844222496</v>
+        <v>-0.09964125034623977</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0264940950168482</v>
+        <v>-0.02649543777461131</v>
       </c>
       <c r="H14" t="n">
-        <v>0.05446596048522404</v>
+        <v>0.05451421364974728</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0578183181110305</v>
+        <v>-0.05767962334487899</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1837945865529658</v>
+        <v>0.1838161347374033</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.1788580033863932</v>
+        <v>-0.1789118752209512</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.1329269583645311</v>
+        <v>-0.1329743527904359</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.06840730406131022</v>
+        <v>-0.06843834262747379</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.05896777848080267</v>
+        <v>-0.05902101239418252</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.2953376706240874</v>
+        <v>-0.295329055351855</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.2644430913235414</v>
+        <v>-0.2643978645464546</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.2389466235245506</v>
+        <v>-0.2388841706093973</v>
       </c>
     </row>
     <row r="15">
@@ -1276,55 +1281,55 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.3629143792905301</v>
+        <v>-0.3629168527812306</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1153107941932486</v>
+        <v>0.1152318886760506</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1732870349476655</v>
+        <v>0.1732404588490479</v>
       </c>
       <c r="E15" t="n">
-        <v>0.02255237928596017</v>
+        <v>0.02253991555209153</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1014526443685277</v>
+        <v>-0.1014055144339805</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1039688511221221</v>
+        <v>0.1040046728592173</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.06343136976200196</v>
+        <v>-0.06334297762858132</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1342740350361031</v>
+        <v>0.1343683883971986</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.3896350778616844</v>
+        <v>-0.3896017385194604</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.2024258365776465</v>
+        <v>-0.2024991134970859</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.1178902286096769</v>
+        <v>-0.1179178103361963</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1930187583784253</v>
+        <v>-0.1930521382934785</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.05896777848080267</v>
+        <v>-0.05902101239418252</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.03289597907794375</v>
+        <v>-0.03292776314358807</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.1210996109163153</v>
+        <v>-0.1210450544413291</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.1930055670227181</v>
+        <v>-0.1929751414894932</v>
       </c>
     </row>
     <row r="16">
@@ -1334,55 +1339,55 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.240043033716194</v>
+        <v>-0.240041652478888</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.2220477856529442</v>
+        <v>-0.2220509313305689</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1034063867575403</v>
+        <v>-0.1034586560844772</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3009063690150895</v>
+        <v>-0.3009819188062258</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.06656412405046591</v>
+        <v>-0.06654841043732869</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2358206499683513</v>
+        <v>-0.2357309035733321</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1484123395333694</v>
+        <v>-0.1483296087384948</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1005609966246396</v>
+        <v>-0.1005366255512958</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.0270555951619233</v>
+        <v>-0.02692265528110705</v>
       </c>
       <c r="K16" t="n">
-        <v>0.08871072898657484</v>
+        <v>0.08865998493314925</v>
       </c>
       <c r="L16" t="n">
-        <v>0.05223704596864914</v>
+        <v>0.05231246629645079</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.07001011577211999</v>
+        <v>-0.06993364975982146</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2953376706240874</v>
+        <v>-0.295329055351855</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.03289597907794375</v>
+        <v>-0.03292776314358807</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.1390458293085042</v>
+        <v>0.1391703769945966</v>
       </c>
       <c r="R16" t="n">
-        <v>0.007146147738917023</v>
+        <v>0.00722477311038023</v>
       </c>
     </row>
     <row r="17">
@@ -1392,55 +1397,55 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.01324026375114542</v>
+        <v>-0.01330740624561528</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.1680245869612388</v>
+        <v>-0.1680519378275852</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2313451186971713</v>
+        <v>-0.2314742367061285</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.09420577337776727</v>
+        <v>-0.0943584122147151</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1322972445931454</v>
+        <v>-0.1322108826535771</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.07221727192292093</v>
+        <v>-0.07219477609322161</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1912360834919151</v>
+        <v>-0.1912657891339729</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1616567900863704</v>
+        <v>-0.1617656976760998</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1450148654958565</v>
+        <v>0.1450683090663101</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0319663306051059</v>
+        <v>0.03204375333207003</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1266375467447297</v>
+        <v>0.1266637001270213</v>
       </c>
       <c r="M17" t="n">
-        <v>0.02959222950174342</v>
+        <v>0.0296466317181022</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2644430913235414</v>
+        <v>-0.2643978645464546</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1210996109163153</v>
+        <v>-0.1210450544413291</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1390458293085042</v>
+        <v>0.1391703769945966</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>-0.04860490386965252</v>
+        <v>-0.04852046936197059</v>
       </c>
     </row>
     <row r="18">
@@ -1450,52 +1455,52 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.1259400640480613</v>
+        <v>0.1258952714727046</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.3191698404367023</v>
+        <v>-0.3192393180553356</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2014782377273373</v>
+        <v>-0.2015918916934702</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1357109229011941</v>
+        <v>-0.1358177859326537</v>
       </c>
       <c r="F18" t="n">
-        <v>0.09091729592942735</v>
+        <v>0.09098756535788116</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1757937360161807</v>
+        <v>-0.1757355241432379</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.02440070246157641</v>
+        <v>-0.02434659855594892</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1070366577892605</v>
+        <v>0.1070796167322649</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.05785683486272918</v>
+        <v>-0.05781818706925114</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.05027295552573411</v>
+        <v>-0.05029834336445638</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.03401914166957559</v>
+        <v>-0.03401029505711925</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1713128387281347</v>
+        <v>-0.1712496303193032</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2389466235245506</v>
+        <v>-0.2388841706093973</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1930055670227181</v>
+        <v>-0.1929751414894932</v>
       </c>
       <c r="P18" t="n">
-        <v>0.007146147738917023</v>
+        <v>0.00722477311038023</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.04860490386965252</v>
+        <v>-0.04852046936197059</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
